--- a/data/S1961_62_FINAL.xlsx
+++ b/data/S1961_62_FINAL.xlsx
@@ -26,8 +26,11 @@
     <sheet name="SERIES" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="CLUBS" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="META" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="TODO" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$8</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -35,7 +38,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,8 +53,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,6 +80,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -86,12 +98,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -16787,7 +16805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16843,6 +16861,115 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>DS-PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1961_62_0665 'Sokol Petřvald (NJ)' prev→CLUB_S1960_61_0575 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1961_62_0369 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NODE_S1961_62_0009</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1961_62_0009 'KVAL  skupina A' (L25, parent=NODE_S1961_62_0008) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NODE_S1961_62_0010</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1961_62_0010 'KVAL  dodatečný zápas' (L25, parent=NODE_S1961_62_0008) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NODE_S1961_62_0011</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1961_62_0011 'KVAL  skupina B' (L25, parent=NODE_S1961_62_0008) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NODE_S1961_62_0012</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1961_62_0012 'KVAL  skupina C' (L25, parent=NODE_S1961_62_0008) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NODE_S1961_62_0013</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1961_62_0013 'KVAL  skupina D' (L25, parent=NODE_S1961_62_0008) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -52505,6 +52632,215 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CLUB_S1961_62_0665</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1961_62_0665 'Sokol Petřvald (NJ)' prev→CLUB_S1960_61_0575 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CLUB_S1961_62_0369</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1961_62_0369 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NODE_S1961_62_0009</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1961_62_0009 'KVAL  skupina A' (L25, parent=NODE_S1961_62_0008) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NODE_S1961_62_0010</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1961_62_0010 'KVAL  dodatečný zápas' (L25, parent=NODE_S1961_62_0008) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NODE_S1961_62_0011</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1961_62_0011 'KVAL  skupina B' (L25, parent=NODE_S1961_62_0008) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NODE_S1961_62_0012</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1961_62_0012 'KVAL  skupina C' (L25, parent=NODE_S1961_62_0008) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NODE_S1961_62_0013</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1961_62_0013 'KVAL  skupina D' (L25, parent=NODE_S1961_62_0008) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F8"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/S1961_62_FINAL.xlsx
+++ b/data/S1961_62_FINAL.xlsx
@@ -29,7 +29,7 @@
     <sheet name="TODO" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -10888,11 +10888,7 @@
           <t>CLUB_S1961_62_0592</t>
         </is>
       </c>
-      <c r="R31" s="3" t="inlineStr">
-        <is>
-          <t>CLUB_S1960_61_0567</t>
-        </is>
-      </c>
+      <c r="R31" s="3" t="n"/>
       <c r="S31" s="3" t="n"/>
       <c r="T31" s="3" t="n"/>
       <c r="U31" s="3" t="n"/>
@@ -10986,11 +10982,7 @@
           <t>CLUB_S1961_62_0594</t>
         </is>
       </c>
-      <c r="R33" s="3" t="inlineStr">
-        <is>
-          <t>CLUB_S1960_61_0567</t>
-        </is>
-      </c>
+      <c r="R33" s="3" t="n"/>
       <c r="S33" s="3" t="n"/>
       <c r="T33" s="3" t="n"/>
       <c r="U33" s="3" t="n"/>
@@ -11133,11 +11125,7 @@
           <t>CLUB_S1961_62_0597</t>
         </is>
       </c>
-      <c r="R36" s="3" t="inlineStr">
-        <is>
-          <t>CLUB_S1960_61_0567</t>
-        </is>
-      </c>
+      <c r="R36" s="3" t="n"/>
       <c r="S36" s="3" t="n"/>
       <c r="T36" s="3" t="n"/>
       <c r="U36" s="3" t="n"/>
@@ -16805,7 +16793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16867,7 +16855,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1961_62_0665 'Sokol Petřvald (NJ)' prev→CLUB_S1960_61_0575 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -16879,7 +16867,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1961_62_0369 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Mladá' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -16889,14 +16877,9 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>NODE_S1961_62_0009</t>
-        </is>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1961_62_0009 'KVAL  skupina A' (L25, parent=NODE_S1961_62_0008) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slavan Lysá nad Labem' → 'Lysá nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -16906,14 +16889,9 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NODE_S1961_62_0010</t>
-        </is>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1961_62_0010 'KVAL  dodatečný zápas' (L25, parent=NODE_S1961_62_0008) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -16923,14 +16901,9 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>NODE_S1961_62_0011</t>
-        </is>
-      </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1961_62_0011 'KVAL  skupina B' (L25, parent=NODE_S1961_62_0008) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Suchdol' → 'Suchdol nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -16940,14 +16913,9 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>NODE_S1961_62_0012</t>
-        </is>
-      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1961_62_0012 'KVAL  skupina C' (L25, parent=NODE_S1961_62_0008) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -16957,17 +16925,216 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>NODE_S1961_62_0013</t>
-        </is>
-      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1961_62_0013 'KVAL  skupina D' (L25, parent=NODE_S1961_62_0008) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1960_61_0236 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Suchdol' → 'Suchdol nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tachov' → 'Bor u Tachova' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Moravská Třebová' → 'Moravská Třebová' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1960_61_0391 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1960_61_0364 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rychnov' → 'Rychnov nad Kněžnou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Horní Staré Město' → 'Staré Město' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí' → 'Veselí nad Moravou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1960_61_0575 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -24092,12 +24259,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Kolín = SC Marimex Kolín (Wiki D42 - registr ustavy 04/2026). Genealogie: Sparta Kolín -&gt; Spartak Tatra Kolín (50.leta - Tatra Kolín = podnik) -&gt; Dukla Kolín (vojensky) -&gt; SK Kolín -&gt; SC Marimex Kolín. KOL = okres Kolín. city Kolín. || Starý Kolín = Jiskra Kara Starý Kolín (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kolín). Kara = podnik. city Starý Kolín.</t>
+          <t>Kolín = SC Marimex Kolín (Wiki D42 - registr ustavy 04/2026). Genealogie: Sparta Kolín -&gt; Spartak Tatra Kolín (50.leta - Tatra Kolín = podnik) -&gt; Dukla Kolín (vojensky) -&gt; SK Kolín -&gt; SC Marimex Kolín. KOL = okres Kolín. city Kolín. || Starý Kolín = Jiskra Kara Starý Kolín (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kolín). Kara = podnik. city Starý Kolín. || TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Kara Starý Kolín</t>
+          <t>Kolín</t>
         </is>
       </c>
     </row>
@@ -26817,12 +26984,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Mladá Boleslav = BK Mladá Boleslav (Wiki D42 - registr ustavy 04/2026). AZNP Mlada Boleslav = Automobilové závody n.p. (Skoda auto). Hlavni chain BK Mlada Boleslav (1924+, predvalecny klub) -&gt; Sokol -&gt; Spartak AZNP -&gt; BK Mlada Boleslav. city Mladá Boleslav.</t>
+          <t>Mladá Boleslav = BK Mladá Boleslav (Wiki D42 - registr ustavy 04/2026). AZNP Mlada Boleslav = Automobilové závody n.p. (Skoda auto). Hlavni chain BK Mlada Boleslav (1924+, predvalecny klub) -&gt; Sokol -&gt; Spartak AZNP -&gt; BK Mlada Boleslav. city Mladá Boleslav. || TBD: city 'Mladá' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Mladá</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -27752,9 +27919,14 @@
           <t>L30</t>
         </is>
       </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slavan Lysá nad Labem' → 'Lysá nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Slavan Lysá nad Labem</t>
+          <t>Lysá nad Labem</t>
         </is>
       </c>
     </row>
@@ -29754,9 +29926,14 @@
           <t>Soutěž</t>
         </is>
       </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>Smrčina Horní Planá</t>
+          <t>Planá</t>
         </is>
       </c>
     </row>
@@ -29798,12 +29975,12 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>Suchdol nL Lužnicí = Tatran Suchdol nL Lužnicí (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Jindřichův Hradec). POZOR: vícero Suchdolů. city Suchdol nad Lužnicí.</t>
+          <t>Suchdol nL Lužnicí = Tatran Suchdol nL Lužnicí (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Jindřichův Hradec). POZOR: vícero Suchdolů. city Suchdol nad Lužnicí. || TBD: city 'Suchdol' → 'Suchdol nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>Suchdol</t>
+          <t>Suchdol nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -30562,12 +30739,12 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>Stranná u Kamenice nL Lipou = TJ Sokol Stranná (Wiki D42 - registr ustavy 04/2026). Vysocina/Pelhrimovsky kraj. POZOR: hraninicni region s Jihocesko - prerodu uzemi. city Stranná u Kamenice nad Lipou.</t>
+          <t>Stranná u Kamenice nL Lipou = TJ Sokol Stranná (Wiki D42 - registr ustavy 04/2026). Vysocina/Pelhrimovsky kraj. POZOR: hraninicni region s Jihocesko - prerodu uzemi. city Stranná u Kamenice nad Lipou. || TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>Stranná u Kamenice nad Lipou</t>
+          <t>Kamenice nad Lipou</t>
         </is>
       </c>
     </row>
@@ -31326,12 +31503,12 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>Hoštice (Wiki D42 - registr ustavy 04/2026). POZOR: vícero Hostic - Stredske Hoštice (Jihocesky, okres Strakonice), Sloupne Hoštice (Jihocesky), Male Hoštice (Severomoravsky, mestska cast Opavy). 'Slovan Male Hoštice' = Severomoravsky! 'Dukla Strelske Hostice' = vojensky Strelske Hostice u Strakonic. city Hoštice.</t>
+          <t>Hoštice (Wiki D42 - registr ustavy 04/2026). POZOR: vícero Hostic - Stredske Hoštice (Jihocesky, okres Strakonice), Sloupne Hoštice (Jihocesky), Male Hoštice (Severomoravsky, mestska cast Opavy). 'Slovan Male Hoštice' = Severomoravsky! 'Dukla Strelske Hostice' = vojensky Strelske Hostice u Strakonic. city Hoštice. || TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>Slovan Malé Hoštice</t>
+          <t>Malé Hoštice</t>
         </is>
       </c>
     </row>
@@ -31781,12 +31958,12 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>Veselí nL Moravou = Lokomotiva Veselí nL Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). POZOR: NE Veselí nL Lužnicí (Jihocesky). city Veselí nad Moravou. || Veselí nL Lužnicí = TJ Tatran/Prefa Veselí nL Lužnicí (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj. POZOR: NE Veselí nL Moravou (Jihomoravsky)! Prefa = prefabrikatovy podnik. ČSD = Československá státní dráha. city Veselí nad Lužnicí.</t>
+          <t>Veselí nL Moravou = Lokomotiva Veselí nL Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). POZOR: NE Veselí nL Lužnicí (Jihocesky). city Veselí nad Moravou. || Veselí nL Lužnicí = TJ Tatran/Prefa Veselí nL Lužnicí (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj. POZOR: NE Veselí nL Moravou (Jihomoravsky)! Prefa = prefabrikatovy podnik. ČSD = Československá státní dráha. city Veselí nad Lužnicí. || TBD: city 'Veselí' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>Veselí</t>
+          <t>Veselí nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -31996,12 +32173,12 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>Hoštice (Wiki D42 - registr ustavy 04/2026). POZOR: vícero Hostic - Stredske Hoštice (Jihocesky, okres Strakonice), Sloupne Hoštice (Jihocesky), Male Hoštice (Severomoravsky, mestska cast Opavy). 'Slovan Male Hoštice' = Severomoravsky! 'Dukla Strelske Hostice' = vojensky Strelske Hostice u Strakonic. city Hoštice.</t>
+          <t>Hoštice (Wiki D42 - registr ustavy 04/2026). POZOR: vícero Hostic - Stredske Hoštice (Jihocesky, okres Strakonice), Sloupne Hoštice (Jihocesky), Male Hoštice (Severomoravsky, mestska cast Opavy). 'Slovan Male Hoštice' = Severomoravsky! 'Dukla Strelske Hostice' = vojensky Strelske Hostice u Strakonic. city Hoštice. || TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>Slovan Malé Hoštice</t>
+          <t>Malé Hoštice</t>
         </is>
       </c>
     </row>
@@ -32038,12 +32215,12 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>Suchdol nL Lužnicí = Tatran Suchdol nL Lužnicí (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Jindřichův Hradec). POZOR: vícero Suchdolů. city Suchdol nad Lužnicí.</t>
+          <t>Suchdol nL Lužnicí = Tatran Suchdol nL Lužnicí (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Jindřichův Hradec). POZOR: vícero Suchdolů. city Suchdol nad Lužnicí. || TBD: city 'Suchdol' → 'Suchdol nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>Suchdol</t>
+          <t>Suchdol nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -34200,12 +34377,12 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>Tachov (Wiki - registr ustavy 04/2026). Zapadocesky/Plzensky kraj. city Tachov.</t>
+          <t>Tachov (Wiki - registr ustavy 04/2026). Zapadocesky/Plzensky kraj. city Tachov. || TBD: city 'Tachov' → 'Bor u Tachova' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>Tachov</t>
+          <t>Bor u Tachova</t>
         </is>
       </c>
     </row>
@@ -37233,12 +37410,12 @@
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t>Moravská Třebová = Slovan/Slavoj Moravská Třebová (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Svitavy). POZOR: NE Třebová Česká (Pardubicky), NE Trebon (Jihocesky). city Moravská Třebová.</t>
+          <t>Moravská Třebová = Slovan/Slavoj Moravská Třebová (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Svitavy). POZOR: NE Třebová Česká (Pardubicky), NE Trebon (Jihocesky). city Moravská Třebová. || TBD: city 'Slovan Moravská Třebová' → 'Moravská Třebová' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>Slovan Moravská Třebová</t>
+          <t>Moravská Třebová</t>
         </is>
       </c>
     </row>
@@ -37898,12 +38075,12 @@
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi.</t>
+          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi. || TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>Rosice u Chrudimi</t>
+          <t>Rosice u Chrasti</t>
         </is>
       </c>
     </row>
@@ -40289,12 +40466,12 @@
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t>Rychnov u Jablonce nad Nisou (Wiki D42 - registr ustavy 04/2026). POZOR: NE Rychnov nad Kněžnou (Královehradecký kraj!). Rychnov u Jablonce nN = Liberecky kraj. D. Rychnov = Dolni Rychnov u Sokolova (=Falknovske doly Sokolov!) city Rychnov.</t>
+          <t>Rychnov u Jablonce nad Nisou (Wiki D42 - registr ustavy 04/2026). POZOR: NE Rychnov nad Kněžnou (Královehradecký kraj!). Rychnov u Jablonce nN = Liberecky kraj. D. Rychnov = Dolni Rychnov u Sokolova (=Falknovske doly Sokolov!) city Rychnov. || TBD: city 'Rychnov' → 'Rychnov nad Kněžnou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J437" t="inlineStr">
         <is>
-          <t>Rychnov</t>
+          <t>Rychnov nad Kněžnou</t>
         </is>
       </c>
     </row>
@@ -40746,12 +40923,12 @@
       </c>
       <c r="I448" t="inlineStr">
         <is>
-          <t>Horní Staré Město = TJ Jiskra Horní Staré Město (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (mestska cast Trutnova!). NE Stare Mesto u UH (Jihomoravsky), NE Stare Mesto u Sumperka. city Trutnov (Horní Staré Město).</t>
+          <t>Horní Staré Město = TJ Jiskra Horní Staré Město (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (mestska cast Trutnova!). NE Stare Mesto u UH (Jihomoravsky), NE Stare Mesto u Sumperka. city Trutnov (Horní Staré Město). || TBD: city 'Horní Staré Město' → 'Staré Město' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J448" t="inlineStr">
         <is>
-          <t>Horní Staré Město</t>
+          <t>Staré Město</t>
         </is>
       </c>
     </row>
@@ -41754,12 +41931,12 @@
       </c>
       <c r="I472" t="inlineStr">
         <is>
-          <t>Veselí nL Moravou = Lokomotiva Veselí nL Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). POZOR: NE Veselí nL Lužnicí (Jihocesky). city Veselí nad Moravou.</t>
+          <t>Veselí nL Moravou = Lokomotiva Veselí nL Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). POZOR: NE Veselí nL Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Veselí' → 'Veselí nad Moravou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J472" t="inlineStr">
         <is>
-          <t>Veselí</t>
+          <t>Veselí nad Moravou</t>
         </is>
       </c>
     </row>
@@ -46293,14 +46470,9 @@
           <t>Přebor II.třídy</t>
         </is>
       </c>
-      <c r="H575" t="inlineStr">
-        <is>
-          <t>CLUB_S1960_61_0567</t>
-        </is>
-      </c>
       <c r="I575" t="inlineStr">
         <is>
-          <t>Karviná = HC Baník Karviná (Wiki - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. POZN: HC Banik Ostrava se pristehoval do Karvine 1995. city Karviná.</t>
+          <t>Karviná = HC Baník Karviná (Wiki - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. POZN: HC Banik Ostrava se pristehoval do Karvine 1995. city Karviná. || TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="J575" t="inlineStr">
@@ -46387,14 +46559,9 @@
           <t>Přebor II.třídy</t>
         </is>
       </c>
-      <c r="H577" t="inlineStr">
-        <is>
-          <t>CLUB_S1960_61_0567</t>
-        </is>
-      </c>
       <c r="I577" t="inlineStr">
         <is>
-          <t>Karviná = HC Baník Karviná (Wiki - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. POZN: HC Banik Ostrava se pristehoval do Karvine 1995. city Karviná.</t>
+          <t>Karviná = HC Baník Karviná (Wiki - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. POZN: HC Banik Ostrava se pristehoval do Karvine 1995. city Karviná. || TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="J577" t="inlineStr">
@@ -46528,14 +46695,9 @@
           <t>III.třída</t>
         </is>
       </c>
-      <c r="H580" t="inlineStr">
-        <is>
-          <t>CLUB_S1960_61_0567</t>
-        </is>
-      </c>
       <c r="I580" t="inlineStr">
         <is>
-          <t>Karviná = HC Baník Karviná (Wiki - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. POZN: HC Banik Ostrava se pristehoval do Karvine 1995. city Karviná.</t>
+          <t>Karviná = HC Baník Karviná (Wiki - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. POZN: HC Banik Ostrava se pristehoval do Karvine 1995. city Karviná. || TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="J580" t="inlineStr">
@@ -50046,12 +50208,12 @@
       </c>
       <c r="I663" t="inlineStr">
         <is>
-          <t>Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves.</t>
+          <t>Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves. || TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J663" t="inlineStr">
         <is>
-          <t>Spišská Nová Ves</t>
+          <t>Nová Ves</t>
         </is>
       </c>
     </row>
@@ -52638,11 +52800,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -52687,21 +52849,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1961_62_0665</t>
+          <t>CLUB_S1961_62_0082</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1961_62_0665 'Sokol Petřvald (NJ)' prev→CLUB_S1960_61_0575 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -52709,21 +52869,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1961_62_0369</t>
+          <t>CLUB_S1961_62_0142</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1961_62_0369 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'Mladá' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -52731,21 +52889,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NODE_S1961_62_0009</t>
+          <t>CLUB_S1961_62_0163</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1961_62_0009 'KVAL  skupina A' (L25, parent=NODE_S1961_62_0008) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: city 'Slavan Lysá nad Labem' → 'Lysá nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -52753,21 +52909,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NODE_S1961_62_0010</t>
+          <t>CLUB_S1961_62_0210</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1961_62_0010 'KVAL  dodatečný zápas' (L25, parent=NODE_S1961_62_0008) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -52775,21 +52929,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NODE_S1961_62_0011</t>
+          <t>CLUB_S1961_62_0211</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1961_62_0011 'KVAL  skupina B' (L25, parent=NODE_S1961_62_0008) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+          <t>TBD: city 'Suchdol' → 'Suchdol nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -52797,21 +52949,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NODE_S1961_62_0012</t>
+          <t>CLUB_S1961_62_0228</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1961_62_0012 'KVAL  skupina C' (L25, parent=NODE_S1961_62_0008) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+          <t>TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -52819,24 +52969,362 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NODE_S1961_62_0013</t>
+          <t>CLUB_S1961_62_0238</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1961_62_0013 'KVAL  skupina D' (L25, parent=NODE_S1961_62_0008) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1960_61_0236 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLUB_S1961_62_0245</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S1961_62_0255</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Veselí' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S1961_62_0260</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CLUB_S1961_62_0261</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Suchdol' → 'Suchdol nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLUB_S1961_62_0313</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Tachov' → 'Bor u Tachova' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLUB_S1961_62_0384</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slovan Moravská Třebová' → 'Moravská Třebová' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S1961_62_0399</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S1961_62_0407</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1960_61_0391 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S1961_62_0427</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1960_61_0364 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S1961_62_0452</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Rychnov' → 'Rychnov nad Kněžnou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLUB_S1961_62_0463</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Horní Staré Město' → 'Staré Město' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLUB_S1961_62_0488</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Veselí' → 'Veselí nad Moravou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLUB_S1961_62_0592</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S1961_62_0594</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLUB_S1961_62_0597</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CLUB_S1961_62_0665</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1960_61_0575 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CLUB_S1961_62_0681</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F8"/>
+  <autoFilter ref="A1:F25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1961_62_FINAL.xlsx
+++ b/data/S1961_62_FINAL.xlsx
@@ -29,7 +29,7 @@
     <sheet name="TODO" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -16793,7 +16793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16987,7 +16987,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Tachov' → 'Bor u Tachova' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Moravská Třebová' → 'Moravská Třebová' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -16999,7 +16999,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Moravská Třebová' → 'Moravská Třebová' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1960_61_0391 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -17011,7 +17011,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1960_61_0364 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -17023,7 +17023,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1960_61_0391 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Horní Staré Město' → 'Staré Město' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -17035,7 +17035,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1960_61_0364 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí' → 'Veselí nad Moravou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -17047,7 +17047,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Rychnov' → 'Rychnov nad Kněžnou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -17059,7 +17059,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Horní Staré Město' → 'Staré Město' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -17071,7 +17071,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí' → 'Veselí nad Moravou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -17083,7 +17083,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1960_61_0575 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -17095,46 +17095,10 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1960_61_0575 (weak, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -17151,7 +17115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K77"/>
+  <dimension ref="A1:L77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17210,6 +17174,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -17252,6 +17221,11 @@
           <t>12 týmů: základní část → finálová skupina 1-6 + o 7.-12. místo. Mistr: Rudá hvězda Brno. Litvínov se udržel (Kolín odřekl účast).</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S1960_61_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -17294,6 +17268,11 @@
           <t>2 skupiny po 12. Kolín nepostoupil do ligy (odřekl účast). Holoubkov/KV baráž.</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NODE_S1960_61_0002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -17336,6 +17315,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S1960_61_0003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -17378,6 +17362,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S1960_61_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -17420,6 +17409,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NODE_S1960_61_0005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17462,6 +17456,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S1960_61_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17504,6 +17503,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S1960_61_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -17551,6 +17555,11 @@
           <t>Kvalifikace o postup do II.ligy; účastní se vítězové krajských přeborů. V kvalifikaci chybí výsledky třetin.</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S1960_61_0008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -17593,6 +17602,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NODE_S1960_61_0009</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -17682,6 +17696,11 @@
           <t>Vítězem severočeského KP byl Litvínov B, ale kvůli sestupu A týmu nemohl hrát II.ligu; kvalifikaci proto hrál Chomutov B.</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NODE_S1960_61_0010</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -17729,6 +17748,11 @@
           <t>Kvalifikace se zúčastnili oba vítězové jihomoravských skupin: Dukla Hodonín a Spartak Královopolská strojírna Brno.</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NODE_S1960_61_0011</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -17771,6 +17795,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NODE_S1960_61_0012</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -17813,6 +17842,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NODE_S1960_61_0013</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -17855,6 +17889,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NODE_S1960_61_0014</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -17897,6 +17936,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NODE_S1960_61_0015</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -17939,6 +17983,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NODE_S1960_61_0016</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -18280,6 +18329,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NODE_S1960_61_0024</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -18322,6 +18376,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NODE_S1960_61_0025</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -18495,6 +18554,11 @@
           <t>Kvalifikace o I.třídu</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>NODE_S1960_61_0028</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -18537,6 +18601,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>NODE_S1960_61_0029</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -18579,6 +18648,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>NODE_S1960_61_0030</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -18705,6 +18779,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>NODE_S1960_61_0033</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -18747,6 +18826,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>NODE_S1960_61_0037</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -18789,6 +18873,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>NODE_S1960_61_0038</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -18962,6 +19051,11 @@
           <t>Kvalifikace</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>NODE_S1960_61_0041</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -19004,6 +19098,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>NODE_S1960_61_0044</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -19046,6 +19145,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>NODE_S1960_61_0045</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -19261,6 +19365,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>NODE_S1960_61_0047</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -19303,6 +19412,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>NODE_S1960_61_0048</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -19345,6 +19459,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>NODE_S1960_61_0049</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -19476,6 +19595,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>NODE_S1960_61_0051</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -19560,6 +19684,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>NODE_S1960_61_0053</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -19985,6 +20114,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>NODE_S1960_61_0064</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -20027,6 +20161,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>NODE_S1960_61_0065</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -20069,6 +20208,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>NODE_S1960_61_0066</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -20111,6 +20255,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>NODE_S1960_61_0067</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -20279,6 +20428,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>NODE_S1960_61_0072</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -20314,6 +20468,11 @@
       <c r="J74" t="inlineStr">
         <is>
           <t>complete</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>NODE_S1960_61_0073</t>
         </is>
       </c>
     </row>
@@ -34377,12 +34536,12 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>Tachov (Wiki - registr ustavy 04/2026). Zapadocesky/Plzensky kraj. city Tachov. || TBD: city 'Tachov' → 'Bor u Tachova' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Tachov (Wiki - registr ustavy 04/2026). Zapadocesky/Plzensky kraj. city Tachov.</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>Bor u Tachova</t>
+          <t>Tachov</t>
         </is>
       </c>
     </row>
@@ -38075,12 +38234,12 @@
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi. || TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi.</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>Rosice u Chrasti</t>
+          <t>Rosice u Chrudimi</t>
         </is>
       </c>
     </row>
@@ -40466,12 +40625,12 @@
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t>Rychnov u Jablonce nad Nisou (Wiki D42 - registr ustavy 04/2026). POZOR: NE Rychnov nad Kněžnou (Královehradecký kraj!). Rychnov u Jablonce nN = Liberecky kraj. D. Rychnov = Dolni Rychnov u Sokolova (=Falknovske doly Sokolov!) city Rychnov. || TBD: city 'Rychnov' → 'Rychnov nad Kněžnou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Rychnov u Jablonce nad Nisou (Wiki D42 - registr ustavy 04/2026). POZOR: NE Rychnov nad Kněžnou (Královehradecký kraj!). Rychnov u Jablonce nN = Liberecky kraj. D. Rychnov = Dolni Rychnov u Sokolova (=Falknovske doly Sokolov!) city Rychnov.</t>
         </is>
       </c>
       <c r="J437" t="inlineStr">
         <is>
-          <t>Rychnov nad Kněžnou</t>
+          <t>Rychnov</t>
         </is>
       </c>
     </row>
@@ -52800,7 +52959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -53074,12 +53233,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S1961_62_0313</t>
+          <t>CLUB_S1961_62_0384</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Tachov' → 'Bor u Tachova' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Slovan Moravská Třebová' → 'Moravská Třebová' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -53094,12 +53253,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S1961_62_0384</t>
+          <t>CLUB_S1961_62_0407</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Slovan Moravská Třebová' → 'Moravská Třebová' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1960_61_0391 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -53114,12 +53273,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S1961_62_0399</t>
+          <t>CLUB_S1961_62_0427</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1960_61_0364 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -53134,12 +53293,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S1961_62_0407</t>
+          <t>CLUB_S1961_62_0463</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1960_61_0391 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Horní Staré Město' → 'Staré Město' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -53154,12 +53313,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S1961_62_0427</t>
+          <t>CLUB_S1961_62_0488</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1960_61_0364 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Veselí' → 'Veselí nad Moravou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -53174,12 +53333,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLUB_S1961_62_0452</t>
+          <t>CLUB_S1961_62_0592</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Rychnov' → 'Rychnov nad Kněžnou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -53194,12 +53353,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLUB_S1961_62_0463</t>
+          <t>CLUB_S1961_62_0594</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Horní Staré Město' → 'Staré Město' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -53214,12 +53373,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLUB_S1961_62_0488</t>
+          <t>CLUB_S1961_62_0597</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Veselí' → 'Veselí nad Moravou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -53234,12 +53393,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLUB_S1961_62_0592</t>
+          <t>CLUB_S1961_62_0665</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1960_61_0575 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -53254,77 +53413,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CLUB_S1961_62_0594</t>
+          <t>CLUB_S1961_62_0681</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>CLUB_S1961_62_0597</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>CLUB_S1961_62_0665</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1960_61_0575 (weak, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>CLUB_S1961_62_0681</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
           <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F25"/>
+  <autoFilter ref="A1:F22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1961_62_FINAL.xlsx
+++ b/data/S1961_62_FINAL.xlsx
@@ -764,7 +764,7 @@
         <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="M13" t="n">
         <v>16</v>
@@ -1481,7 +1481,7 @@
         <v>15</v>
       </c>
       <c r="J14" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>

--- a/data/S1961_62_FINAL.xlsx
+++ b/data/S1961_62_FINAL.xlsx
@@ -17115,7 +17115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L77"/>
+  <dimension ref="A1:N77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17177,6 +17177,16 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>prev_node_id</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
         </is>
       </c>
     </row>

--- a/data/S1961_62_FINAL.xlsx
+++ b/data/S1961_62_FINAL.xlsx
@@ -17409,6 +17409,16 @@
           <t>NODE_S1961_62_0001</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>NODE_S1961_62_0006</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>NODE_S1961_62_0007</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17423,6 +17433,14 @@
         <is>
           <t>NODE_S1960_61_0005</t>
         </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>12 týmů</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -17456,6 +17474,8 @@
           <t>NODE_S1961_62_0001</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17470,6 +17490,14 @@
         <is>
           <t>NODE_S1960_61_0006</t>
         </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -17503,6 +17531,8 @@
           <t>NODE_S1961_62_0001</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17517,6 +17547,14 @@
         <is>
           <t>NODE_S1960_61_0007</t>
         </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>7.–12. ZČ</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -19323,6 +19361,8 @@
           <t>NODE_S1961_62_0042</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19332,6 +19372,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="49">
@@ -19731,6 +19779,8 @@
           <t>NODE_S1961_62_0053</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19740,6 +19790,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="58">
@@ -19815,6 +19873,8 @@
           <t>NODE_S1961_62_0053</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19824,6 +19884,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="60">

--- a/data/S1961_62_FINAL.xlsx
+++ b/data/S1961_62_FINAL.xlsx
@@ -17474,8 +17474,6 @@
           <t>NODE_S1961_62_0001</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17531,8 +17529,6 @@
           <t>NODE_S1961_62_0001</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19361,8 +19357,6 @@
           <t>NODE_S1961_62_0042</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19779,8 +19773,6 @@
           <t>NODE_S1961_62_0053</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19873,8 +19865,6 @@
           <t>NODE_S1961_62_0053</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>2-1-0</t>
